--- a/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Théo a dessiné dans le salon. Ses jambes ont encore envie de bouger. Maman dit : on va dehors. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au jardin avec maman. Dehors, l'herbe est fraîche. Un oiseau chante. Théo court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Théo lance le cerceau. Maman le renvoie. Parce qu'il joue dehors, son corps est content. Théo dit : je joue dehors, avec un adulte. Maman sourit. Ils jouent un moment. Théo sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Théo a pu bouger. Théo a joué dehors. Un adulte était avec lui.</t>
+          <t>Théo a dessiné dans le salon. Ses jambes ont encore envie de bouger. On va dehors. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au jardin avec maman. Dehors, l'herbe est fraîche. Un oiseau chante. Théo court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Théo lance le cerceau. Maman le renvoie. Parce qu'il joue dehors, son corps est content. Je joue dehors, avec un adulte. Maman sourit. Ils jouent un moment. Théo sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Théo a pu bouger. Théo a joué dehors. Un adulte était avec lui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Théo a dessiné dans le salon. Ses jambes ont encore envie de bouger.
+maman|On va dehors.
+narrateur|Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au jardin avec maman. Dehors, l'herbe est fraîche. Un oiseau chante. Théo court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Théo lance le cerceau. Maman le renvoie. Parce qu'il joue dehors, son corps est content.
+enfant-m|Je joue dehors, avec un adulte. Maman sourit. Ils jouent un moment.
+narrateur|Théo sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Théo a pu bouger. Théo a joué dehors. Un adulte était avec lui.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Théo veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Théo a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Théo boit de l'eau. Il range le cerceau. Merci, dit-il à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Théo sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Théo a pu bouger. Théo a joué dehors. Un adulte était avec lui.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Théo veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Théo a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Théo boit de l'eau. Il range le cerceau. Merci, dit-il à maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Théo joue dehors au jardin</t>
+          <t>L'ombre du figuier</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'ombre du figuier fait un bateau. Le cerceau bleu attend. Nino et maman vont au jardin. Ils jouent dehors. Un adulte est là.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Théo a dessiné dans le salon. Ses jambes ont encore envie de bouger. On va dehors. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au jardin avec maman. Dehors, l'herbe est fraîche. Un oiseau chante. Théo court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Théo lance le cerceau. Maman le renvoie. Parce qu'il joue dehors, son corps est content. Je joue dehors, avec un adulte. Maman sourit. Ils jouent un moment. Théo sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Théo a pu bouger. Théo a joué dehors. Un adulte était avec lui.</t>
+          <t>L'ombre du figuier fait un bateau sur l'herbe. Une abeille visite le romarin. Le cerceau bleu s'appuie contre le tronc. Le portillon du jardin grince un peu. Ça sent la terre tiède. En ce moment, Nino a dessiné. Ses jambes ont encore envie. Maman. On va dehors ? On va dehors. Ils mettent les chaussures près de la porte. Une chaussure, puis l'autre. Ils prennent le cerceau bleu. Il est lisse, un peu poussiéreux. Ils poussent le portillon. Dehors, l'herbe est fraîche. Un oiseau chante. Nino court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Nino lance le cerceau. Maman le renvoie. Le cerceau roule, puis tombe. Encore ! Encore. Parce qu'il joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Nino. Tu bouges, et je suis là. Ils jouent un moment. Nino sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Nino a pu bouger. Nino a joué dehors. Un adulte était avec lui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Théo a dessiné dans le salon. Ses jambes ont encore envie de bouger.
+          <t>narrateur|L'ombre du figuier fait un bateau sur l'herbe.
+narrateur|Une abeille visite le romarin.
+narrateur|Le cerceau bleu s'appuie contre le tronc.
+narrateur|Le portillon du jardin grince un peu.
+narrateur|Ça sent la terre tiède.
+narrateur|En ce moment, Nino a dessiné.
+narrateur|Ses jambes ont encore envie.
+enfant-m|Maman.
+enfant-m|On va dehors ?
 maman|On va dehors.
-narrateur|Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au jardin avec maman. Dehors, l'herbe est fraîche. Un oiseau chante. Théo court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Théo lance le cerceau. Maman le renvoie. Parce qu'il joue dehors, son corps est content.
-enfant-m|Je joue dehors, avec un adulte. Maman sourit. Ils jouent un moment.
-narrateur|Théo sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Théo a pu bouger. Théo a joué dehors. Un adulte était avec lui.</t>
+narrateur|Ils mettent les chaussures près de la porte.
+narrateur|Une chaussure, puis l'autre.
+narrateur|Ils prennent le cerceau bleu.
+narrateur|Il est lisse, un peu poussiéreux.
+narrateur|Ils poussent le portillon.
+narrateur|Dehors, l'herbe est fraîche.
+narrateur|Un oiseau chante.
+narrateur|Nino court jusqu'au pommier.
+narrateur|Maman reste près de lui.
+narrateur|C'est un adulte.
+narrateur|Nino lance le cerceau.
+narrateur|Maman le renvoie.
+narrateur|Le cerceau roule, puis tombe.
+enfant-m|Encore !
+maman|Encore.
+narrateur|Parce qu'il joue dehors, son corps est content.
+enfant-m|Je joue dehors, avec un adulte.
+maman|Bravo, Nino.
+maman|Tu bouges, et je suis là.
+narrateur|Ils jouent un moment.
+narrateur|Nino sent ses joues chaudes.
+narrateur|Puis ils rentrent ensemble.
+narrateur|Parce que maman était là, Nino a pu bouger.
+narrateur|Nino a joué dehors.
+narrateur|Un adulte était avec lui.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,oiseau</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Théo veut bouger. Où joue-t-il ?</t>
+          <t>Nino veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1551,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Théo veut bouger. Où joue-t-il ?</t>
+          <t>narrateur|Nino veut bouger.
+narrateur|Où joue-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1580,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Théo a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+          <t>Nino a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Tu as fait du bon travail. Dehors, avec un adulte. Oui, maman. Dans le jardin. Le cerceau a un peu d'herbe. Nino le tourne. Il est encore bleu. Tu as couru jusqu'au pommier ? Oui. L'herbe était froide. Maman rit tout doux. Les joues de Nino sont chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1724,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Théo a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+          <t>narrateur|Nino a joué dehors.
+narrateur|Maman, un adulte, était avec lui.
+narrateur|Le corps a bougé.
+narrateur|C'est bien.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|Dehors, avec un adulte.
+enfant-m|Oui, maman.
+enfant-m|Dans le jardin.
+narrateur|Le cerceau a un peu d'herbe.
+narrateur|Nino le tourne.
+narrateur|Il est encore bleu.
+maman|Tu as couru jusqu'au pommier ?
+enfant-m|Oui.
+enfant-m|L'herbe était froide.
+narrateur|Maman rit tout doux.
+narrateur|Les joues de Nino sont chaudes.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Théo boit de l'eau. Il range le cerceau. Merci, dit-il à maman.</t>
+          <t>Nino boit de l'eau. La tasse est fraîche. Il range le cerceau. Le cerceau retrouve le figuier. Merci, maman. Merci, Nino. Le portillon grince encore. Une dernière fois. L'abeille n'est plus là. L'ombre du bateau a bougé. On rentre les chaussures ? Oui. Nino enlève une chaussure. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1904,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Théo boit de l'eau. Il range le cerceau. Merci, dit-il à maman.</t>
+          <t>narrateur|Nino boit de l'eau.
+narrateur|La tasse est fraîche.
+narrateur|Il range le cerceau.
+narrateur|Le cerceau retrouve le figuier.
+enfant-m|Merci, maman.
+maman|Merci, Nino.
+narrateur|Le portillon grince encore.
+narrateur|Une dernière fois.
+narrateur|L'abeille n'est plus là.
+narrateur|L'ombre du bateau a bougé.
+maman|On rentre les chaussures ?
+enfant-m|Oui.
+narrateur|Nino enlève une chaussure.
+narrateur|Puis l'autre.
+narrateur|Ses pieds sont contents.
+maman|On reste un peu ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. Tu as fait du bon travail. L'ombre a fait un bateau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2088,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai joué dehors.
+enfant-m|Avec un adulte.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|L'ombre a fait un bateau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du figuier fait un bateau sur l'herbe. Une abeille visite le romarin. Le cerceau bleu s'appuie contre le tronc. Le portillon du jardin grince un peu. Ça sent la terre tiède. En ce moment, Nino a dessiné. Ses jambes ont encore envie. Maman. On va dehors ? On va dehors. Ils mettent les chaussures près de la porte. Une chaussure, puis l'autre. Ils prennent le cerceau bleu. Il est lisse, un peu poussiéreux. Ils poussent le portillon. Dehors, l'herbe est fraîche. Un oiseau chante. Nino court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Nino lance le cerceau. Maman le renvoie. Le cerceau roule, puis tombe. Encore ! Encore. Parce qu'il joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Nino. Tu bouges, et je suis là. Ils jouent un moment. Nino sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Nino a pu bouger. Nino a joué dehors. Un adulte était avec lui.</t>
+          <t>L'ombre du figuier fait un bateau sur l'herbe. Une abeille visite le romarin. Le cerceau bleu s'appuie contre le tronc. Le portillon du jardin grince un peu. Ça sent la terre tiède. À la fenêtre, un crayon bleu attend. Un dessin de figuier n'est pas fini. En ce moment, Nino pose le crayon. Ses jambes ont encore envie. Maman. On va dehors ? On va dehors. Ils mettent les chaussures près de la porte. Une chaussure, puis l'autre. Ils prennent le cerceau bleu. Il est lisse, un peu poussiéreux. Ils poussent le portillon. Dehors, l'herbe est fraîche. Un oiseau chante. Nino court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Nino lance le cerceau. Maman le renvoie. Le cerceau roule, puis tombe. Encore ! Encore. Parce qu'il joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Nino. Tu bouges, et je suis là. Tu as fini de lancer le cerceau ? Encore un peu. Encore un peu, d'accord. Ils jouent un moment. Nino sent ses joues chaudes. Puis ils rentrent ensemble. Je suis avec toi, Nino. Oui, maman. Nino donne la main. Nino a joué dehors. Un adulte était avec lui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Théo a dessiné dans le salon. Ses jambes ont encore envie de bouger. Maman dit : on va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au jardin avec maman. Dehors, l'herbe est fraîche. Un oiseau chante. Théo court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Théo lance le cerceau. Maman le renvoie. Parce qu'il joue dehors, son corps est content. Théo dit : je joue dehors, avec un adulte. Maman sourit. Ils jouent un moment. Théo sent ses joues chaudes. Puis ils rentrent ensemble. Parce que maman était là, Théo a pu bouger. Théo a joué dehors. Un adulte était avec lui.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'ombre du figuier fait un bateau sur l'herbe. Une abeille visite le romarin. Le cerceau bleu s'appuie contre le tronc. Le portillon du jardin grince un peu. Ça sent la terre tiède. À la fenêtre, un crayon bleu attend. Un dessin de figuier n'est pas fini. En ce moment, Nino pose le crayon. Ses jambes ont encore envie. Maman. On va dehors ? On va dehors. Ils mettent les chaussures près de la porte. Une chaussure, puis l'autre. Ils prennent le cerceau bleu. Il est lisse, un peu poussiéreux. Ils poussent le portillon. Dehors, l'herbe est fraîche. Un oiseau chante. Nino court jusqu'au pommier. Maman reste près de lui. C'est un adulte. Nino lance le cerceau. Maman le renvoie. Le cerceau roule, puis tombe. Encore ! Encore. Parce qu'il joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Nino. Tu bouges, et je suis là. Tu as fini de lancer le cerceau ? Encore un peu. Encore un peu, d'accord. Ils jouent un moment. Nino sent ses joues chaudes. Puis ils rentrent ensemble. Je suis avec toi, Nino. Oui, maman. Nino donne la main. Nino a joué dehors. Un adulte était avec lui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1334,7 +1334,9 @@
 narrateur|Le cerceau bleu s'appuie contre le tronc.
 narrateur|Le portillon du jardin grince un peu.
 narrateur|Ça sent la terre tiède.
-narrateur|En ce moment, Nino a dessiné.
+narrateur|À la fenêtre, un crayon bleu attend.
+narrateur|Un dessin de figuier n'est pas fini.
+narrateur|En ce moment, Nino pose le crayon.
 narrateur|Ses jambes ont encore envie.
 enfant-m|Maman.
 enfant-m|On va dehors ?
@@ -1358,10 +1360,15 @@
 enfant-m|Je joue dehors, avec un adulte.
 maman|Bravo, Nino.
 maman|Tu bouges, et je suis là.
+maman|Tu as fini de lancer le cerceau ?
+enfant-m|Encore un peu.
+maman|Encore un peu, d'accord.
 narrateur|Ils jouent un moment.
 narrateur|Nino sent ses joues chaudes.
 narrateur|Puis ils rentrent ensemble.
-narrateur|Parce que maman était là, Nino a pu bouger.
+maman|Je suis avec toi, Nino.
+enfant-m|Oui, maman.
+narrateur|Nino donne la main.
 narrateur|Nino a joué dehors.
 narrateur|Un adulte était avec lui.</t>
         </is>
@@ -1400,7 +1407,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Théo veut bouger. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1555,7 +1562,6 @@
 narrateur|Où joue-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1580,12 +1586,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Tu as fait du bon travail. Dehors, avec un adulte. Oui, maman. Dans le jardin. Le cerceau a un peu d'herbe. Nino le tourne. Il est encore bleu. Tu as couru jusqu'au pommier ? Oui. L'herbe était froide. Maman rit tout doux. Les joues de Nino sont chaudes.</t>
+          <t>Nino a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Dehors, avec un adulte. Oui, maman. Dans le jardin. Le cerceau a un peu d'herbe. Nino le tourne. Il est encore bleu. Tu as couru jusqu'au pommier ? Oui. L'herbe était froide. Tu as bien couru. Tes joues sont chaudes. Les joues de Nino sont chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Théo a joué &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a joué dehors. Maman, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Dehors, avec un adulte. Oui, maman. Dans le jardin. Le cerceau a un peu d'herbe. Nino le tourne. Il est encore bleu. Tu as couru jusqu'au pommier ? Oui. L'herbe était froide. Tu as bien couru. Tes joues sont chaudes. Les joues de Nino sont chaudes.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1729,7 +1735,6 @@
 narrateur|Le corps a bougé.
 narrateur|C'est bien.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 maman|Dehors, avec un adulte.
 enfant-m|Oui, maman.
 enfant-m|Dans le jardin.
@@ -1739,11 +1744,11 @@
 maman|Tu as couru jusqu'au pommier ?
 enfant-m|Oui.
 enfant-m|L'herbe était froide.
-narrateur|Maman rit tout doux.
+maman|Tu as bien couru.
+maman|Tes joues sont chaudes.
 narrateur|Les joues de Nino sont chaudes.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1768,12 +1773,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino boit de l'eau. La tasse est fraîche. Il range le cerceau. Le cerceau retrouve le figuier. Merci, maman. Merci, Nino. Le portillon grince encore. Une dernière fois. L'abeille n'est plus là. L'ombre du bateau a bougé. On rentre les chaussures ? Oui. Nino enlève une chaussure. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, maman.</t>
+          <t>Nino boit de l'eau. La tasse est fraîche. Il range le cerceau. Le cerceau retrouve le figuier. Merci, maman. Merci, Nino. Le portillon grince encore. Une dernière fois. L'abeille n'est plus là. L'ombre du bateau a bougé. On rentre les chaussures ? Oui. Nino enlève une chaussure. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, maman. Le crayon bleu attend encore. Le dessin, on le finit plus tard. D'accord. L'ombre du figuier a bougé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Théo boit de l'eau. Il range le cerceau. Merci, dit-il à maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino boit de l'eau. La tasse est fraîche. Il range le cerceau. Le cerceau retrouve le figuier. Merci, maman. Merci, Nino. Le portillon grince encore. Une dernière fois. L'abeille n'est plus là. L'ombre du bateau a bougé. On rentre les chaussures ? Oui. Nino enlève une chaussure. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, maman. Le crayon bleu attend encore. Le dessin, on le finit plus tard. D'accord. L'ombre du figuier a bougé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1920,10 +1925,13 @@
 narrateur|Puis l'autre.
 narrateur|Ses pieds sont contents.
 maman|On reste un peu ?
-enfant-m|Oui, maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+enfant-m|Oui, maman.
+narrateur|Le crayon bleu attend encore.
+maman|Le dessin, on le finit plus tard.
+enfant-m|D'accord.
+narrateur|L'ombre du figuier a bougé.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1948,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai joué dehors. Avec un adulte. Bravo. Tu as fait du bon travail. L'ombre a fait un bateau. L'histoire est finie.</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. L'ombre a fait un bateau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. L'ombre a fait un bateau.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2091,12 +2099,9 @@
           <t>enfant-m|J'ai joué dehors.
 enfant-m|Avec un adulte.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-maman|L'ombre a fait un bateau.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|L'ombre a fait un bateau.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2115,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-02.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Théo, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
